--- a/DOSSIES_MULTIFORMATO/FHEMOAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FHEMOAM/dossie.xlsx
@@ -662,7 +662,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025NE0001739</t>
+          <t>2025NE0001736</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>818.66</v>
+        <v>817.14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -681,14 +681,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto: "Prestação de serviços de desenvolvimento e execução de sistemas - PRODAM-RH".-Fundação de Hematologia e Hemoterapia do Amazonas; -Período: 01/09/21 a 30/09/21; -Par</t>
+          <t>-Sem cobertura contratual;-Objeto: "Prestação de serviços de desenvolvimento e execução de sistemas - PRODAM-RH".-Fundação de Hematologia e Hemoterapia do Amazonas; -Período: 01/05/21 a 31/05/21; -Par</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025NE0001738</t>
+          <t>2025NE0001737</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -714,7 +714,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025NE0001737</t>
+          <t>2025NE0001738</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -740,7 +740,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025NE0001736</t>
+          <t>2025NE0001739</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>817.14</v>
+        <v>818.66</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto: "Prestação de serviços de desenvolvimento e execução de sistemas - PRODAM-RH".-Fundação de Hematologia e Hemoterapia do Amazonas; -Período: 01/05/21 a 31/05/21; -Par</t>
+          <t>-Sem cobertura contratual;-Objeto: "Prestação de serviços de desenvolvimento e execução de sistemas - PRODAM-RH".-Fundação de Hematologia e Hemoterapia do Amazonas; -Período: 01/09/21 a 30/09/21; -Par</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026NE0000145</t>
+          <t>2026NE0000146</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>339.54</v>
+        <v>338.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -849,14 +849,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto: “ Serviços Prestados na execução de Sistemas – PRODAM-RH para geração de Folha Especial de Pagamento do Piso Salarial da Enfermagem”;-Fundação de Hematologia e Hemot</t>
+          <t>-Sem cobertura contratual;-Objeto: “ Serviços Prestados na execução de Sistemas – PRODAM-RH para geração de Folha Especial de Pagamento do Piso Salarial da Enfermagem”; -Fundação de Hematologia e Hemo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026NE0000147</t>
+          <t>2026NE0000148</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>352.86</v>
+        <v>352.02</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026NE0000148</t>
+          <t>2026NE0000147</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>352.02</v>
+        <v>352.86</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026NE0000146</t>
+          <t>2026NE0000145</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>338.7</v>
+        <v>339.54</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -939,14 +939,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto: “ Serviços Prestados na execução de Sistemas – PRODAM-RH para geração de Folha Especial de Pagamento do Piso Salarial da Enfermagem”; -Fundação de Hematologia e Hemo</t>
+          <t>-Sem cobertura contratual;-Objeto: “ Serviços Prestados na execução de Sistemas – PRODAM-RH para geração de Folha Especial de Pagamento do Piso Salarial da Enfermagem”;-Fundação de Hematologia e Hemot</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025NE0001329</t>
+          <t>2025NE0001330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>359.04</v>
+        <v>364.65</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto: "Prestação de serviços de desenvolvimento e execução de sistemas - PRODAM-RH, destinados à geração da Folha Especial de Pagamento do Piso Salarial da Enfermagem". -F</t>
+          <t>-Sem cobertura contratual;-Objeto: "Prestação de serviços de desenvolvimento e execução de sistemas - PRODAM-RH, destinados à geração da Folha Especial de Pagamento do Piso Salarial da Enfermagem".-Fu</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025NE0001330</t>
+          <t>2025NE0001329</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>364.65</v>
+        <v>359.04</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto: "Prestação de serviços de desenvolvimento e execução de sistemas - PRODAM-RH, destinados à geração da Folha Especial de Pagamento do Piso Salarial da Enfermagem".-Fu</t>
+          <t>-Sem cobertura contratual;-Objeto: "Prestação de serviços de desenvolvimento e execução de sistemas - PRODAM-RH, destinados à geração da Folha Especial de Pagamento do Piso Salarial da Enfermagem". -F</t>
         </is>
       </c>
     </row>
@@ -1050,21 +1050,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2018NE01193</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>27/2017</t>
-        </is>
-      </c>
+          <t>2018NE01173</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>21/09/2018</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3700</v>
+        <v>3375.74</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1073,7 +1069,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Prestação de Serviço Execução de Sistema PRODAM-RH</t>
+          <t>ANULAÇÃO TOTAL DA NE Nº 152/2018.</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1102,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2018NE01173</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>2018NE01193</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>27/2017</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>21/09/2018</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3375.74</v>
+        <v>3700</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE Nº 152/2018.</t>
+          <t>Prestação de Serviço Execução de Sistema PRODAM-RH</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025NE0001143</t>
+          <t>2025NE0001144</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>364.65</v>
+        <v>367.17</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025NE0001147</t>
+          <t>2025NE0001142</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>367.17</v>
+        <v>359.04</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1215,14 +1215,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto:“ “Prestação de Serviços de Processamento de Dados Execucao de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Funcionario processado em folha mensal ”; -Fundação</t>
+          <t xml:space="preserve">-Sem cobertura contratual;-Objeto: “Prestação de Serviços de Processamento de Dados Execucao de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Funcionario processado em folha mensal ”; -Fundação </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025NE0001146</t>
+          <t>2025NE0001145</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>355.11</v>
+        <v>361.98</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto:“ “Prestação de Serviços de Processamento de Dados Execucao de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Funcionario processado em folha mensal ”; -Fundação</t>
+          <t>-Sem cobertura contratual;-Objeto: “Prestação de Serviços de Processamento de Dados Execucao de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Funcionario processado em folha mensal ”;-Fundação d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025NE0001145</t>
+          <t>2025NE0001146</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>361.98</v>
+        <v>355.11</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto: “Prestação de Serviços de Processamento de Dados Execucao de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Funcionario processado em folha mensal ”;-Fundação d</t>
+          <t>-Sem cobertura contratual;-Objeto:“ “Prestação de Serviços de Processamento de Dados Execucao de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Funcionario processado em folha mensal ”; -Fundação</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025NE0001142</t>
+          <t>2025NE0001147</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>359.04</v>
+        <v>367.17</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1305,14 +1305,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">-Sem cobertura contratual;-Objeto: “Prestação de Serviços de Processamento de Dados Execucao de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Funcionario processado em folha mensal ”; -Fundação </t>
+          <t>-Sem cobertura contratual;-Objeto:“ “Prestação de Serviços de Processamento de Dados Execucao de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Funcionario processado em folha mensal ”; -Fundação</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025NE0001144</t>
+          <t>2025NE0001143</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>367.17</v>
+        <v>364.65</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025NE0001405</t>
+          <t>2025NE0001404</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18.23</v>
+        <v>17.95</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-Anulação Parcial da Nota de Empenho nº 1330/2025, conforme despacho da Subgerência de Liquidação e Pagamento desta Fundação. -Processo nº 1632/2025-43.</t>
+          <t>-Anulação Parcial da Nota de Empenho nº 1329/2025, conforme despacho da Subgerência de Liquidação e Pagamento desta Fundação. -Processo nº 1632/2025-43.</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025NE0001404</t>
+          <t>2025NE0001405</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.95</v>
+        <v>18.23</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1469,14 +1469,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-Anulação Parcial da Nota de Empenho nº 1329/2025, conforme despacho da Subgerência de Liquidação e Pagamento desta Fundação. -Processo nº 1632/2025-43.</t>
+          <t>-Anulação Parcial da Nota de Empenho nº 1330/2025, conforme despacho da Subgerência de Liquidação e Pagamento desta Fundação. -Processo nº 1632/2025-43.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026NE0000266</t>
+          <t>2026NE0000267</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>352.02</v>
+        <v>339.54</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1495,14 +1495,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anulação da NE 182/2026 para fins de ajustes.</t>
+          <t>Anulação da NE 145/2026 para correção da Natureza de Despesa.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026NE0000269</t>
+          <t>2026NE0000270</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>352.02</v>
+        <v>339.54</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1525,14 +1525,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto: “ Serviços Prestados na execução de Sistemas – PRODAM-RH para geração de Folha Especial de Pagamento do Piso Salarial da Enfermagem”; -Fundação de Hematologia e Hemo</t>
+          <t>-Sem cobertura contratual;-Objeto: “ Serviços Prestados na execução de Sistemas – PRODAM-RH para geração de Folha Especial de Pagamento do Piso Salarial da Enfermagem”;-Fundação de Hematologia e Hemot</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026NE0000270</t>
+          <t>2026NE0000269</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>339.54</v>
+        <v>352.02</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1555,14 +1555,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto: “ Serviços Prestados na execução de Sistemas – PRODAM-RH para geração de Folha Especial de Pagamento do Piso Salarial da Enfermagem”;-Fundação de Hematologia e Hemot</t>
+          <t>-Sem cobertura contratual;-Objeto: “ Serviços Prestados na execução de Sistemas – PRODAM-RH para geração de Folha Especial de Pagamento do Piso Salarial da Enfermagem”; -Fundação de Hematologia e Hemo</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026NE0000267</t>
+          <t>2026NE0000266</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>339.54</v>
+        <v>352.02</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anulação da NE 145/2026 para correção da Natureza de Despesa.</t>
+          <t>Anulação da NE 182/2026 para fins de ajustes.</t>
         </is>
       </c>
     </row>
@@ -1696,10 +1696,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026NE0000181</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>2026NE0000182</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P.174/2024</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>03/03/2026</t>
@@ -1715,21 +1719,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Para correção na natureza de despesa.</t>
+          <t>-Sem cobertura contratual;-Objeto: “ Serviços Prestados na execução de Sistemas – PRODAM-RH para geração de Folha Especial de Pagamento do Piso Salarial da Enfermagem”; -Fundação de Hematologia e Hemo</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026NE0000182</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>P.174/2024</t>
-        </is>
-      </c>
+          <t>2026NE0000181</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>03/03/2026</t>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-Sem cobertura contratual;-Objeto: “ Serviços Prestados na execução de Sistemas – PRODAM-RH para geração de Folha Especial de Pagamento do Piso Salarial da Enfermagem”; -Fundação de Hematologia e Hemo</t>
+          <t>Para correção na natureza de despesa.</t>
         </is>
       </c>
     </row>
@@ -1804,10 +1804,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2018NE00204</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>2018NE00281</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>27/2017</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
           <t>01/03/2018</t>
@@ -1823,21 +1827,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE CITADA, PARA FINS DE ATENDER ALTERAÇÃO NA natureza de despesa de TIC antigA</t>
+          <t>Contratação de empresa especializada para a execução do Sistema PRODAM-RH - Cadastro e Folha de Pagamento de Pessoal. Referente a Parcela de janeiro/2018</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2018NE00281</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>27/2017</t>
-        </is>
-      </c>
+          <t>2018NE00204</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>01/03/2018</t>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para a execução do Sistema PRODAM-RH - Cadastro e Folha de Pagamento de Pessoal. Referente a Parcela de janeiro/2018</t>
+          <t>ANULAÇÃO TOTAL DA NE CITADA, PARA FINS DE ATENDER ALTERAÇÃO NA natureza de despesa de TIC antigA</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/FHEMOAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/FHEMOAM/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2030-08-31</t>
         </is>
       </c>
     </row>
